--- a/data/PPGDfull.xlsx
+++ b/data/PPGDfull.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthingocmai/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthingocmai/Documents/Thạc sĩ/modelAI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513BB927-1303-2F42-9468-10C3F2789128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C00D4B-52FA-AD42-B4AA-8EAC04E20541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ma tran PPGD" sheetId="8" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/data/PPGDfull.xlsx
+++ b/data/PPGDfull.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthingocmai/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyenthingocmai/Documents/Thạc sĩ/modelAI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513BB927-1303-2F42-9468-10C3F2789128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF17E1D-F4C1-A84F-BEC8-DE53F78BD30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ma tran PPGD" sheetId="8" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
